--- a/data/trans_bre/P1416-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P1416-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,92</t>
+          <t>4,72</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>84,45%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,32</t>
+          <t>0,32; 4,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 3,15</t>
+          <t>-0,29; 3,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,57</t>
+          <t>0,98; 4,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 6,34</t>
+          <t>2,2; 7,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,7; 107,16</t>
+          <t>4,54; 103,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,07; 120,0</t>
+          <t>-6,44; 123,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,24; 298,83</t>
+          <t>25,05; 275,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,23; 142,86</t>
+          <t>31,08; 172,92</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-3,7%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 5,9</t>
+          <t>1,77; 5,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,74</t>
+          <t>1,32; 4,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,15; 5,29</t>
+          <t>1,95; 5,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 3,05</t>
+          <t>-1,22; 2,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,18; 98,09</t>
+          <t>21,96; 96,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,58; 100,37</t>
+          <t>20,4; 97,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,92; 120,97</t>
+          <t>34,79; 121,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-27,03; 34,76</t>
+          <t>-9,85; 27,13</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,15</t>
+          <t>6,24</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>74,39%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 6,95</t>
+          <t>-1,17; 7,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 7,11</t>
+          <t>-0,39; 7,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 6,5</t>
+          <t>-1,43; 6,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,79; 9,25</t>
+          <t>3,07; 9,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 99,71</t>
+          <t>-14,04; 93,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 141,06</t>
+          <t>-6,1; 147,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 98,62</t>
+          <t>-14,32; 89,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28,09; 146,44</t>
+          <t>29,39; 138,64</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,44</t>
+          <t>2,31</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>23,84%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,21</t>
+          <t>1,51; 4,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,45</t>
+          <t>1,04; 3,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,34</t>
+          <t>1,89; 4,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 3,62</t>
+          <t>0,74; 3,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,84; 69,12</t>
+          <t>21,13; 68,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,66; 75,65</t>
+          <t>17,96; 74,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,81; 100,34</t>
+          <t>33,02; 94,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 46,2</t>
+          <t>7,21; 42,87</t>
         </is>
       </c>
     </row>
